--- a/output/pdf_financials_xlsx/RSH.xlsx
+++ b/output/pdf_financials_xlsx/RSH.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.493677</v>
+        <v>-0.493677</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.257573</v>
+        <v>-0.257573</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.493677</v>
+        <v>-0.493677</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.257573</v>
+        <v>-0.257573</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.493677</v>
+        <v>-0.493677</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.257573</v>
+        <v>-0.257573</v>
       </c>
     </row>
     <row r="24">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-24.68385</v>
+        <v>24.68385</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.493677</v>
+        <v>-0.493677</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.257573</v>
+        <v>-0.257573</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.493677</v>
+        <v>-0.493677</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.257573</v>
+        <v>-0.257573</v>
       </c>
     </row>
     <row r="30">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.257573</v>
+        <v>-0.257573</v>
       </c>
     </row>
     <row r="70">
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.493677</v>
+        <v>-0.493677</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.524243</v>
+        <v>-0.524243</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RSH.xlsx
+++ b/output/pdf_financials_xlsx/RSH.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0067</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018259</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00682</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.493677</v>
+        <v>-0.486977</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.524243</v>
+        <v>-0.505984</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.257573</v>
+        <v>-0.250753</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.493677</v>
+        <v>-0.486977</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.524243</v>
+        <v>-0.505984</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.257573</v>
+        <v>-0.250753</v>
       </c>
     </row>
     <row r="30">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
